--- a/docs/evidencia/sprint2/S2_IT_checklist.xlsx
+++ b/docs/evidencia/sprint2/S2_IT_checklist.xlsx
@@ -425,7 +425,7 @@
         <v>Fecha de auditoría</v>
       </c>
       <c r="B3" s="1" t="str">
-        <v>2026-10-28T17:33:48.684Z</v>
+        <v>2026-10-28T18:12:15.695Z</v>
       </c>
     </row>
     <row r="4">
